--- a/Data/2035/GoRES/Input/Xlsx/Transmission.xlsx
+++ b/Data/2035/GoRES/Input/Xlsx/Transmission.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C271"/>
+  <dimension ref="A1:C263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4046,12 +4046,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4136,12 +4136,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4151,12 +4151,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4166,12 +4166,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4181,12 +4181,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4241,12 +4241,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4256,12 +4256,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4271,7 +4271,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4286,12 +4286,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4301,12 +4301,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4316,12 +4316,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4331,12 +4331,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4346,135 +4346,15 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="C265" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C266" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="C267" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="C269" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C270" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="C271" t="n">
         <v>0.97</v>
       </c>
     </row>
@@ -4489,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B124"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5901,72 +5781,36 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES432</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>ES618</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>ES422</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>ES432</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Italy</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7908,27 +7752,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -7938,12 +7782,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -7953,76 +7797,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>1500</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -8036,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9957,127 +9741,67 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>97.416</v>
+        <v>122.262</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>98.892</v>
+        <v>30.5286</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>272.322</v>
+        <v>53.9478</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>30.5286</v>
+        <v>57.1704</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>53.9478</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>57.1704</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
         <v>128.0676</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>215.7666</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>285.3846</v>
       </c>
     </row>
   </sheetData>
@@ -10091,7 +9815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D941"/>
+  <dimension ref="A1:D913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26009,12 +25733,12 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -26027,12 +25751,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -26045,12 +25769,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -26063,12 +25787,12 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -26081,12 +25805,12 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -26099,12 +25823,12 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -26117,12 +25841,12 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -26135,12 +25859,12 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C893" t="n">
@@ -26153,12 +25877,12 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -26171,12 +25895,12 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -26189,12 +25913,12 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -26207,12 +25931,12 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C897" t="n">
@@ -26225,12 +25949,12 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -26243,12 +25967,12 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C899" t="n">
@@ -26261,12 +25985,12 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -26279,12 +26003,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C901" t="n">
@@ -26297,12 +26021,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -26315,12 +26039,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -26333,12 +26057,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -26351,12 +26075,12 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C905" t="n">
@@ -26369,12 +26093,12 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -26387,12 +26111,12 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -26405,12 +26129,12 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -26423,12 +26147,12 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -26441,12 +26165,12 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -26459,12 +26183,12 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -26477,12 +26201,12 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -26495,522 +26219,18 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C913" t="n">
         <v>7</v>
       </c>
       <c r="D913" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="914">
-      <c r="A914" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B914" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C914" t="n">
-        <v>1</v>
-      </c>
-      <c r="D914" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="915">
-      <c r="A915" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B915" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C915" t="n">
-        <v>2</v>
-      </c>
-      <c r="D915" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="916">
-      <c r="A916" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B916" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C916" t="n">
-        <v>3</v>
-      </c>
-      <c r="D916" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="917">
-      <c r="A917" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B917" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C917" t="n">
-        <v>4</v>
-      </c>
-      <c r="D917" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="918">
-      <c r="A918" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B918" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C918" t="n">
-        <v>5</v>
-      </c>
-      <c r="D918" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="919">
-      <c r="A919" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B919" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C919" t="n">
-        <v>6</v>
-      </c>
-      <c r="D919" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="920">
-      <c r="A920" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B920" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C920" t="n">
-        <v>7</v>
-      </c>
-      <c r="D920" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="921">
-      <c r="A921" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B921" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C921" t="n">
-        <v>1</v>
-      </c>
-      <c r="D921" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="922">
-      <c r="A922" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B922" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C922" t="n">
-        <v>2</v>
-      </c>
-      <c r="D922" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="923">
-      <c r="A923" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B923" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C923" t="n">
-        <v>3</v>
-      </c>
-      <c r="D923" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="924">
-      <c r="A924" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B924" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C924" t="n">
-        <v>4</v>
-      </c>
-      <c r="D924" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="925">
-      <c r="A925" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B925" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C925" t="n">
-        <v>5</v>
-      </c>
-      <c r="D925" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="926">
-      <c r="A926" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B926" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C926" t="n">
-        <v>6</v>
-      </c>
-      <c r="D926" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="927">
-      <c r="A927" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B927" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C927" t="n">
-        <v>7</v>
-      </c>
-      <c r="D927" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="928">
-      <c r="A928" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B928" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C928" t="n">
-        <v>1</v>
-      </c>
-      <c r="D928" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="929">
-      <c r="A929" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B929" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C929" t="n">
-        <v>2</v>
-      </c>
-      <c r="D929" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="930">
-      <c r="A930" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B930" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C930" t="n">
-        <v>3</v>
-      </c>
-      <c r="D930" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="931">
-      <c r="A931" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B931" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C931" t="n">
-        <v>4</v>
-      </c>
-      <c r="D931" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="932">
-      <c r="A932" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B932" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C932" t="n">
-        <v>5</v>
-      </c>
-      <c r="D932" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="933">
-      <c r="A933" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B933" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C933" t="n">
-        <v>6</v>
-      </c>
-      <c r="D933" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="934">
-      <c r="A934" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B934" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C934" t="n">
-        <v>7</v>
-      </c>
-      <c r="D934" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="935">
-      <c r="A935" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B935" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C935" t="n">
-        <v>1</v>
-      </c>
-      <c r="D935" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="936">
-      <c r="A936" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B936" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C936" t="n">
-        <v>2</v>
-      </c>
-      <c r="D936" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="937">
-      <c r="A937" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B937" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C937" t="n">
-        <v>3</v>
-      </c>
-      <c r="D937" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="938">
-      <c r="A938" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B938" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C938" t="n">
-        <v>4</v>
-      </c>
-      <c r="D938" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="939">
-      <c r="A939" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B939" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C939" t="n">
-        <v>5</v>
-      </c>
-      <c r="D939" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="940">
-      <c r="A940" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B940" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C940" t="n">
-        <v>6</v>
-      </c>
-      <c r="D940" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="941">
-      <c r="A941" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B941" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C941" t="n">
-        <v>7</v>
-      </c>
-      <c r="D941" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -27025,7 +26245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28946,127 +28166,67 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>396</v>
+        <v>497</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>402</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1107</v>
+        <v>219.3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>124.1</v>
+        <v>232.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>219.3</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>232.4</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
         <v>520.6</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>877.1</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>1160.1</v>
       </c>
     </row>
   </sheetData>
@@ -29534,7 +28694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D745"/>
+  <dimension ref="A1:D717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41306,7 +40466,7 @@
         <v>1</v>
       </c>
       <c r="D655" t="n">
-        <v>12200</v>
+        <v>17300</v>
       </c>
     </row>
     <row r="656">
@@ -41324,7 +40484,7 @@
         <v>2</v>
       </c>
       <c r="D656" t="n">
-        <v>12900</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="657">
@@ -41342,7 +40502,7 @@
         <v>3</v>
       </c>
       <c r="D657" t="n">
-        <v>12900</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="658">
@@ -41360,7 +40520,7 @@
         <v>4</v>
       </c>
       <c r="D658" t="n">
-        <v>12900</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="659">
@@ -41378,7 +40538,7 @@
         <v>5</v>
       </c>
       <c r="D659" t="n">
-        <v>12900</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="660">
@@ -41396,7 +40556,7 @@
         <v>6</v>
       </c>
       <c r="D660" t="n">
-        <v>12900</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="661">
@@ -41414,511 +40574,511 @@
         <v>7</v>
       </c>
       <c r="D661" t="n">
-        <v>12900</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C662" t="n">
         <v>1</v>
       </c>
       <c r="D662" t="n">
-        <v>6300</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C663" t="n">
         <v>2</v>
       </c>
       <c r="D663" t="n">
-        <v>6900</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C664" t="n">
         <v>3</v>
       </c>
       <c r="D664" t="n">
-        <v>6900</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C665" t="n">
         <v>4</v>
       </c>
       <c r="D665" t="n">
-        <v>6900</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C666" t="n">
         <v>5</v>
       </c>
       <c r="D666" t="n">
-        <v>6900</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C667" t="n">
         <v>6</v>
       </c>
       <c r="D667" t="n">
-        <v>6900</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C668" t="n">
         <v>7</v>
       </c>
       <c r="D668" t="n">
-        <v>6900</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C669" t="n">
         <v>1</v>
       </c>
       <c r="D669" t="n">
-        <v>5100</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C670" t="n">
         <v>2</v>
       </c>
       <c r="D670" t="n">
-        <v>6300</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C671" t="n">
         <v>3</v>
       </c>
       <c r="D671" t="n">
-        <v>6300</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C672" t="n">
         <v>4</v>
       </c>
       <c r="D672" t="n">
-        <v>6300</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C673" t="n">
         <v>5</v>
       </c>
       <c r="D673" t="n">
-        <v>6300</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C674" t="n">
         <v>6</v>
       </c>
       <c r="D674" t="n">
-        <v>6300</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C675" t="n">
         <v>7</v>
       </c>
       <c r="D675" t="n">
-        <v>6300</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C676" t="n">
         <v>1</v>
       </c>
       <c r="D676" t="n">
-        <v>1513</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C677" t="n">
         <v>2</v>
       </c>
       <c r="D677" t="n">
-        <v>1513</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C678" t="n">
         <v>3</v>
       </c>
       <c r="D678" t="n">
-        <v>1513</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C679" t="n">
         <v>4</v>
       </c>
       <c r="D679" t="n">
-        <v>1513</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C680" t="n">
         <v>5</v>
       </c>
       <c r="D680" t="n">
-        <v>1513</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C681" t="n">
         <v>6</v>
       </c>
       <c r="D681" t="n">
-        <v>1513</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C682" t="n">
         <v>7</v>
       </c>
       <c r="D682" t="n">
-        <v>1513</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="C683" t="n">
         <v>1</v>
       </c>
       <c r="D683" t="n">
-        <v>2140</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="C684" t="n">
         <v>2</v>
       </c>
       <c r="D684" t="n">
-        <v>2140</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="C685" t="n">
         <v>3</v>
       </c>
       <c r="D685" t="n">
-        <v>2140</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="C686" t="n">
         <v>4</v>
       </c>
       <c r="D686" t="n">
-        <v>2140</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="C687" t="n">
         <v>5</v>
       </c>
       <c r="D687" t="n">
-        <v>2140</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="C688" t="n">
         <v>6</v>
       </c>
       <c r="D688" t="n">
-        <v>2140</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="C689" t="n">
         <v>7</v>
       </c>
       <c r="D689" t="n">
-        <v>2140</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="690">
@@ -41929,14 +41089,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="C690" t="n">
         <v>1</v>
       </c>
       <c r="D690" t="n">
-        <v>1970</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="691">
@@ -41947,14 +41107,14 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="C691" t="n">
         <v>2</v>
       </c>
       <c r="D691" t="n">
-        <v>1970</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="692">
@@ -41965,14 +41125,14 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="C692" t="n">
         <v>3</v>
       </c>
       <c r="D692" t="n">
-        <v>1970</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="693">
@@ -41983,14 +41143,14 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="C693" t="n">
         <v>4</v>
       </c>
       <c r="D693" t="n">
-        <v>1970</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="694">
@@ -42001,14 +41161,14 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="C694" t="n">
         <v>5</v>
       </c>
       <c r="D694" t="n">
-        <v>1970</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="695">
@@ -42019,14 +41179,14 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="C695" t="n">
         <v>6</v>
       </c>
       <c r="D695" t="n">
-        <v>1970</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="696">
@@ -42037,895 +41197,391 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="C696" t="n">
         <v>7</v>
       </c>
       <c r="D696" t="n">
-        <v>1970</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C697" t="n">
         <v>1</v>
       </c>
       <c r="D697" t="n">
-        <v>2030</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C698" t="n">
         <v>2</v>
       </c>
       <c r="D698" t="n">
-        <v>2030</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C699" t="n">
         <v>3</v>
       </c>
       <c r="D699" t="n">
-        <v>2030</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C700" t="n">
         <v>4</v>
       </c>
       <c r="D700" t="n">
-        <v>2030</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C701" t="n">
         <v>5</v>
       </c>
       <c r="D701" t="n">
-        <v>2030</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C702" t="n">
         <v>6</v>
       </c>
       <c r="D702" t="n">
-        <v>2030</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C703" t="n">
         <v>7</v>
       </c>
       <c r="D703" t="n">
-        <v>2030</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C704" t="n">
         <v>1</v>
       </c>
       <c r="D704" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C705" t="n">
         <v>2</v>
       </c>
       <c r="D705" t="n">
-        <v>1440</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C706" t="n">
         <v>3</v>
       </c>
       <c r="D706" t="n">
-        <v>1440</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C707" t="n">
         <v>4</v>
       </c>
       <c r="D707" t="n">
-        <v>1440</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C708" t="n">
         <v>5</v>
       </c>
       <c r="D708" t="n">
-        <v>1440</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C709" t="n">
         <v>6</v>
       </c>
       <c r="D709" t="n">
-        <v>1440</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C710" t="n">
         <v>7</v>
       </c>
       <c r="D710" t="n">
-        <v>1440</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C711" t="n">
         <v>1</v>
       </c>
       <c r="D711" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C712" t="n">
         <v>2</v>
       </c>
       <c r="D712" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C713" t="n">
         <v>3</v>
       </c>
       <c r="D713" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C714" t="n">
         <v>4</v>
       </c>
       <c r="D714" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C715" t="n">
         <v>5</v>
       </c>
       <c r="D715" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C716" t="n">
         <v>6</v>
       </c>
       <c r="D716" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C717" t="n">
         <v>7</v>
       </c>
       <c r="D717" t="n">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C718" t="n">
-        <v>1</v>
-      </c>
-      <c r="D718" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B719" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C719" t="n">
-        <v>2</v>
-      </c>
-      <c r="D719" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B720" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C720" t="n">
-        <v>3</v>
-      </c>
-      <c r="D720" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C721" t="n">
-        <v>4</v>
-      </c>
-      <c r="D721" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C722" t="n">
-        <v>5</v>
-      </c>
-      <c r="D722" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C723" t="n">
-        <v>6</v>
-      </c>
-      <c r="D723" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C724" t="n">
-        <v>7</v>
-      </c>
-      <c r="D724" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>ES220</t>
-        </is>
-      </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C725" t="n">
-        <v>1</v>
-      </c>
-      <c r="D725" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>ES220</t>
-        </is>
-      </c>
-      <c r="B726" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C726" t="n">
-        <v>2</v>
-      </c>
-      <c r="D726" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>ES220</t>
-        </is>
-      </c>
-      <c r="B727" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C727" t="n">
-        <v>3</v>
-      </c>
-      <c r="D727" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>ES220</t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C728" t="n">
-        <v>4</v>
-      </c>
-      <c r="D728" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>ES220</t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C729" t="n">
-        <v>5</v>
-      </c>
-      <c r="D729" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>ES220</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C730" t="n">
-        <v>6</v>
-      </c>
-      <c r="D730" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>ES220</t>
-        </is>
-      </c>
-      <c r="B731" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C731" t="n">
-        <v>7</v>
-      </c>
-      <c r="D731" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B732" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C732" t="n">
-        <v>1</v>
-      </c>
-      <c r="D732" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B733" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C733" t="n">
-        <v>2</v>
-      </c>
-      <c r="D733" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B734" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C734" t="n">
-        <v>3</v>
-      </c>
-      <c r="D734" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B735" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C735" t="n">
-        <v>4</v>
-      </c>
-      <c r="D735" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B736" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C736" t="n">
-        <v>5</v>
-      </c>
-      <c r="D736" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B737" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C737" t="n">
-        <v>6</v>
-      </c>
-      <c r="D737" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B738" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C738" t="n">
-        <v>7</v>
-      </c>
-      <c r="D738" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B739" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C739" t="n">
-        <v>1</v>
-      </c>
-      <c r="D739" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B740" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C740" t="n">
-        <v>2</v>
-      </c>
-      <c r="D740" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B741" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C741" t="n">
-        <v>3</v>
-      </c>
-      <c r="D741" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B742" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C742" t="n">
-        <v>4</v>
-      </c>
-      <c r="D742" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B743" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C743" t="n">
-        <v>5</v>
-      </c>
-      <c r="D743" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B744" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C744" t="n">
-        <v>6</v>
-      </c>
-      <c r="D744" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B745" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C745" t="n">
-        <v>7</v>
-      </c>
-      <c r="D745" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42940,7 +41596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D941"/>
+  <dimension ref="A1:D913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58744,7 +57400,7 @@
         <v>1</v>
       </c>
       <c r="D879" t="n">
-        <v>12200</v>
+        <v>17300</v>
       </c>
     </row>
     <row r="880">
@@ -58762,7 +57418,7 @@
         <v>2</v>
       </c>
       <c r="D880" t="n">
-        <v>13900</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="881">
@@ -58780,7 +57436,7 @@
         <v>3</v>
       </c>
       <c r="D881" t="n">
-        <v>13900</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="882">
@@ -58798,7 +57454,7 @@
         <v>4</v>
       </c>
       <c r="D882" t="n">
-        <v>13900</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="883">
@@ -58816,7 +57472,7 @@
         <v>5</v>
       </c>
       <c r="D883" t="n">
-        <v>13900</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="884">
@@ -58834,7 +57490,7 @@
         <v>6</v>
       </c>
       <c r="D884" t="n">
-        <v>13900</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="885">
@@ -58852,1014 +57508,510 @@
         <v>7</v>
       </c>
       <c r="D885" t="n">
-        <v>13900</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C886" t="n">
         <v>1</v>
       </c>
       <c r="D886" t="n">
-        <v>6300</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C887" t="n">
         <v>2</v>
       </c>
       <c r="D887" t="n">
-        <v>7900</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C888" t="n">
         <v>3</v>
       </c>
       <c r="D888" t="n">
-        <v>7900</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C889" t="n">
         <v>4</v>
       </c>
       <c r="D889" t="n">
-        <v>7900</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C890" t="n">
         <v>5</v>
       </c>
       <c r="D890" t="n">
-        <v>7900</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C891" t="n">
         <v>6</v>
       </c>
       <c r="D891" t="n">
-        <v>7900</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C892" t="n">
         <v>7</v>
       </c>
       <c r="D892" t="n">
-        <v>7900</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C893" t="n">
         <v>1</v>
       </c>
       <c r="D893" t="n">
-        <v>5100</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C894" t="n">
         <v>2</v>
       </c>
       <c r="D894" t="n">
-        <v>6300</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C895" t="n">
         <v>3</v>
       </c>
       <c r="D895" t="n">
-        <v>6300</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C896" t="n">
         <v>4</v>
       </c>
       <c r="D896" t="n">
-        <v>6300</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C897" t="n">
         <v>5</v>
       </c>
       <c r="D897" t="n">
-        <v>6300</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C898" t="n">
         <v>6</v>
       </c>
       <c r="D898" t="n">
-        <v>6300</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C899" t="n">
         <v>7</v>
       </c>
       <c r="D899" t="n">
-        <v>6300</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C900" t="n">
         <v>1</v>
       </c>
       <c r="D900" t="n">
-        <v>3013</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C901" t="n">
         <v>2</v>
       </c>
       <c r="D901" t="n">
-        <v>3013</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C902" t="n">
         <v>3</v>
       </c>
       <c r="D902" t="n">
-        <v>3013</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C903" t="n">
         <v>4</v>
       </c>
       <c r="D903" t="n">
-        <v>3013</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C904" t="n">
         <v>5</v>
       </c>
       <c r="D904" t="n">
-        <v>3013</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C905" t="n">
         <v>6</v>
       </c>
       <c r="D905" t="n">
-        <v>3013</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C906" t="n">
         <v>7</v>
       </c>
       <c r="D906" t="n">
-        <v>3013</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C907" t="n">
         <v>1</v>
       </c>
       <c r="D907" t="n">
-        <v>3640</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C908" t="n">
         <v>2</v>
       </c>
       <c r="D908" t="n">
-        <v>3640</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C909" t="n">
         <v>3</v>
       </c>
       <c r="D909" t="n">
-        <v>3640</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C910" t="n">
         <v>4</v>
       </c>
       <c r="D910" t="n">
-        <v>3640</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C911" t="n">
         <v>5</v>
       </c>
       <c r="D911" t="n">
-        <v>3640</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C912" t="n">
         <v>6</v>
       </c>
       <c r="D912" t="n">
-        <v>3640</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C913" t="n">
         <v>7</v>
       </c>
       <c r="D913" t="n">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="914">
-      <c r="A914" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B914" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C914" t="n">
-        <v>1</v>
-      </c>
-      <c r="D914" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="915">
-      <c r="A915" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B915" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C915" t="n">
-        <v>2</v>
-      </c>
-      <c r="D915" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="916">
-      <c r="A916" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B916" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C916" t="n">
-        <v>3</v>
-      </c>
-      <c r="D916" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="917">
-      <c r="A917" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B917" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C917" t="n">
-        <v>4</v>
-      </c>
-      <c r="D917" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="918">
-      <c r="A918" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B918" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C918" t="n">
-        <v>5</v>
-      </c>
-      <c r="D918" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="919">
-      <c r="A919" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B919" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C919" t="n">
-        <v>6</v>
-      </c>
-      <c r="D919" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="920">
-      <c r="A920" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B920" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C920" t="n">
-        <v>7</v>
-      </c>
-      <c r="D920" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="921">
-      <c r="A921" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B921" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C921" t="n">
-        <v>1</v>
-      </c>
-      <c r="D921" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="922">
-      <c r="A922" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B922" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C922" t="n">
-        <v>2</v>
-      </c>
-      <c r="D922" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="923">
-      <c r="A923" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B923" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C923" t="n">
-        <v>3</v>
-      </c>
-      <c r="D923" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="924">
-      <c r="A924" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B924" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C924" t="n">
-        <v>4</v>
-      </c>
-      <c r="D924" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="925">
-      <c r="A925" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B925" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C925" t="n">
-        <v>5</v>
-      </c>
-      <c r="D925" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="926">
-      <c r="A926" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B926" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C926" t="n">
-        <v>6</v>
-      </c>
-      <c r="D926" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="927">
-      <c r="A927" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B927" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C927" t="n">
-        <v>7</v>
-      </c>
-      <c r="D927" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="928">
-      <c r="A928" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B928" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C928" t="n">
-        <v>1</v>
-      </c>
-      <c r="D928" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="929">
-      <c r="A929" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B929" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C929" t="n">
-        <v>2</v>
-      </c>
-      <c r="D929" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="930">
-      <c r="A930" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B930" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C930" t="n">
-        <v>3</v>
-      </c>
-      <c r="D930" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="931">
-      <c r="A931" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B931" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C931" t="n">
-        <v>4</v>
-      </c>
-      <c r="D931" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="932">
-      <c r="A932" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B932" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C932" t="n">
-        <v>5</v>
-      </c>
-      <c r="D932" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="933">
-      <c r="A933" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B933" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C933" t="n">
-        <v>6</v>
-      </c>
-      <c r="D933" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="934">
-      <c r="A934" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B934" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C934" t="n">
-        <v>7</v>
-      </c>
-      <c r="D934" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="935">
-      <c r="A935" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B935" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C935" t="n">
-        <v>1</v>
-      </c>
-      <c r="D935" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="936">
-      <c r="A936" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B936" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C936" t="n">
-        <v>2</v>
-      </c>
-      <c r="D936" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="937">
-      <c r="A937" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B937" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C937" t="n">
-        <v>3</v>
-      </c>
-      <c r="D937" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="938">
-      <c r="A938" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B938" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C938" t="n">
-        <v>4</v>
-      </c>
-      <c r="D938" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="939">
-      <c r="A939" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B939" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C939" t="n">
-        <v>5</v>
-      </c>
-      <c r="D939" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="940">
-      <c r="A940" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B940" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C940" t="n">
-        <v>6</v>
-      </c>
-      <c r="D940" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="941">
-      <c r="A941" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B941" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C941" t="n">
-        <v>7</v>
-      </c>
-      <c r="D941" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -59874,7 +58026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61801,12 +59953,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -61816,12 +59968,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -61831,12 +59983,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -61846,75 +59998,15 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>ES213</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>ES511</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>ES523</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
         <v>40</v>
       </c>
     </row>
@@ -61929,7 +60021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63826,75 +61918,45 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>98.892</v>
+        <v>30.5286</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>272.322</v>
+        <v>53.9478</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>30.5286</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>ES432</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>53.9478</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>ES618</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>ES422</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
         <v>57.1704</v>
       </c>
     </row>
